--- a/Test cases/Casus 3 - Incorrect/Timetable Casus 3.xlsx
+++ b/Test cases/Casus 3 - Incorrect/Timetable Casus 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/872575_fontys_nl/Documents/Documenten/Python/PJ5 Dataset/Casus 3 - Incorrect/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/Test cases/Casus 3 - Incorrect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_085DC7CF9342980E6235547658DFFEBCAC5D9814" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5FCAD0F-A704-493D-B3F1-24576B2B4F24}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_085DC7CF9342980E6235547658DFFEBCAC5D9814" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C9D89B8-38A5-4AFD-BCDF-D16DB4FEA482}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
   <si>
-    <t>start location</t>
-  </si>
-  <si>
-    <t>start time</t>
-  </si>
-  <si>
     <t>end</t>
   </si>
   <si>
@@ -71,6 +65,12 @@
   </si>
   <si>
     <t>07:21</t>
+  </si>
+  <si>
+    <t>departure_time</t>
+  </si>
+  <si>
+    <t>start</t>
   </si>
 </sst>
 </file>
@@ -89,6 +89,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -133,7 +134,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,27 +439,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>400</v>
@@ -466,13 +467,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>401</v>
@@ -480,13 +481,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>401</v>
@@ -494,13 +495,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>401</v>
@@ -508,13 +509,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>401</v>
@@ -522,13 +523,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>401</v>
@@ -536,13 +537,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8">
         <v>401</v>
@@ -550,13 +551,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>401</v>
@@ -564,13 +565,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <v>401</v>
@@ -578,13 +579,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <v>401</v>
